--- a/config/sdt_templates/CRS181MI_API.xlsx
+++ b/config/sdt_templates/CRS181MI_API.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\w10itasv\Documents\DataMigrationTool_v1.2\config\sdt_templates\"/>
@@ -21,7 +21,7 @@
     <sheet name="API_CRS181MI_Add" sheetId="2" r:id="rId6"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -935,13 +935,6 @@
     <t>MESSAGE</t>
   </si>
   <si>
-    <t>Result
-Message</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
     <t>FILE</t>
   </si>
   <si>
@@ -954,10 +947,14 @@
     <t>TX15</t>
   </si>
   <si>
+    <t>Result
+Message</t>
+  </si>
+  <si>
     <t>Table</t>
   </si>
   <si>
-    <t>User defined-field 1</t>
+    <t>User-defined field 1 - item</t>
   </si>
   <si>
     <t>Description</t>
@@ -966,33 +963,36 @@
     <t>Name</t>
   </si>
   <si>
+    <t>no</t>
+  </si>
+  <si>
     <t>yes</t>
   </si>
   <si>
-    <t>User-defined field 1 - item</t>
+    <t>ROWREF</t>
+  </si>
+  <si>
+    <t>TXID</t>
+  </si>
+  <si>
+    <t>Row
+Reference</t>
+  </si>
+  <si>
+    <t>Text identity</t>
   </si>
   <si>
     <t>FILE#</t>
   </si>
   <si>
-    <t>TXID</t>
-  </si>
-  <si>
-    <t>Text identity</t>
-  </si>
-  <si>
-    <t>ROWREF</t>
-  </si>
-  <si>
-    <t>Row
-Reference</t>
+    <t>User defined-field 1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1406,63 +1406,63 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8A05A76-3036-4A66-9DA4-D2058403D14E}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="5" width="8.88671875" style="2"/>
+    <col min="2" max="5" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="112.9">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="C2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" ht="112.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4" t="s">
+    <row r="3" spans="1:5" ht="15" thickBot="1">
+      <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:5" ht="15" thickTop="1"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:E3" xr:uid="{E3C8E670-729D-416E-A8F6-07E04C802C80}">
@@ -1477,54 +1477,54 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB087D05-BB1C-4C17-8424-CC0F3469062C}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="6" width="8.88671875" style="2"/>
+    <col min="2" max="6" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="7" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="112.9">
+      <c r="A2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="112.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" ht="15" thickBot="1">
       <c r="A3" s="5" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>11</v>
@@ -1542,7 +1542,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:6" ht="15" thickTop="1"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:F3" xr:uid="{72101F51-1CEC-4CCC-8776-05C0A1B0B51A}">
@@ -1557,36 +1557,36 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC7686C2-8422-44EF-8011-DB6BEE683A84}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="3" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="112.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="112.9">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15" thickBot="1">
       <c r="A3" s="5" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>11</v>
@@ -1595,7 +1595,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:3" ht="15" thickTop="1"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:C3" xr:uid="{49578E1C-D7AB-4E89-AD0D-BDD50DF0666E}">
@@ -1610,60 +1610,60 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6DAD80DB-599A-45E6-9B7E-1A3DE6ED2855}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="7" width="8.88671875" style="2"/>
+    <col min="2" max="7" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:7" ht="112.9">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="112.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>12</v>
-      </c>
       <c r="D2" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>9</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>10</v>
       </c>
       <c r="G2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="15" thickBot="1">
       <c r="A3" s="5" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>11</v>
@@ -1684,7 +1684,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:7" ht="15" thickTop="1"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:G3" xr:uid="{A48C6651-6D68-408C-A1EE-F16B97DF4432}">
@@ -1699,36 +1699,36 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1B96858-A531-4603-AC93-283B1C124425}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="3" width="8.88671875" style="2"/>
+    <col min="2" max="3" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="112.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" ht="112.9">
       <c r="A2" s="3" t="s">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>12</v>
-      </c>
     </row>
-    <row r="3" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" ht="15" thickBot="1">
       <c r="A3" s="5" t="s">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>11</v>
@@ -1737,7 +1737,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:3" ht="15" thickTop="1"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:C3" xr:uid="{49EC6242-27F5-4BF7-B509-6FC602D66208}">
@@ -1752,63 +1752,63 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8960ED6-CDFC-4A7D-9738-9762DF945F9B}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="5" width="8.88671875" style="2"/>
+    <col min="2" max="5" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="88.15">
+      <c r="A2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>6</v>
       </c>
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" ht="88.2" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="4" t="s">
+    <row r="3" spans="1:5" ht="15" thickBot="1">
+      <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
+      <c r="B3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
+    <row r="4" spans="1:5" ht="15" thickTop="1"/>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="list" errorStyle="warning" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A3:E3" xr:uid="{A46DEEF7-B92E-4791-BC1C-9D88AAFCCB0B}">
@@ -1823,7 +1823,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C76CCD8-9403-45D8-A939-23C024BC4B45}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
